--- a/demo/saas_projection_v12.xlsx
+++ b/demo/saas_projection_v12.xlsx
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>D5*Assumptions!$B$6</f>
+        <f>D5*Assumptions!$B$6*1.12</f>
         <v/>
       </c>
       <c r="E6" s="8">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>-C4*(1-0.71)</f>
+        <f>-C4*(1-Assumptions!B8)</f>
         <v/>
       </c>
     </row>
